--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="390">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L'entrée Produit de santé permet de décrire un médicament ou un vaccin.</t>
+    <t>FrMedicationDocument permet de décrire un médicament ou un vaccin.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -718,53 +718,40 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.id</t>
+    <t>Medication.code.coding.extension:translation.value[x].id</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].id</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.extension</t>
+    <t>Medication.code.coding.extension:translation.value[x].extension</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].extension</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.id</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.id</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.id</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.extension</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.extension</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.extension</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.system</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.system</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.system</t>
@@ -797,7 +784,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.version</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.version</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.version</t>
@@ -821,7 +808,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.code</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.code</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.code</t>
@@ -845,7 +832,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.display</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.display</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.display</t>
@@ -869,7 +856,7 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.coding.userSelected</t>
+    <t>Medication.code.coding.extension:translation.value[x].coding.userSelected</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].coding.userSelected</t>
@@ -900,7 +887,7 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>Medication.code.coding.extension:translation.value[x]:valueCodeableConcept.text</t>
+    <t>Medication.code.coding.extension:translation.value[x].text</t>
   </si>
   <si>
     <t>Medication.code.coding.extension.value[x].text</t>
@@ -1561,12 +1548,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="78.859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="60.1484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.16796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4410,17 +4397,19 @@
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AC25" s="2"/>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4449,20 +4438,18 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>87</v>
@@ -4477,13 +4464,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4534,7 +4521,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4546,13 +4533,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4563,21 +4550,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4589,15 +4576,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4634,31 +4623,31 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4675,14 +4664,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4698,21 +4687,23 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4748,19 +4739,19 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4772,27 +4763,27 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4803,7 +4794,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4812,23 +4803,19 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4876,50 +4863,50 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4931,15 +4918,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4976,31 +4965,31 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -5017,21 +5006,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5040,21 +5029,23 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5078,63 +5069,61 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5157,20 +5146,18 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5194,11 +5181,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5216,7 +5205,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5234,21 +5223,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5271,18 +5260,18 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5330,7 +5319,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5348,21 +5337,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5385,17 +5374,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5444,7 +5433,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5462,21 +5451,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5499,17 +5488,19 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5558,7 +5549,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5576,21 +5567,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5613,19 +5604,19 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5674,7 +5665,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5692,21 +5683,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5729,19 +5720,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>284</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5790,7 +5781,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5808,21 +5799,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5845,20 +5836,18 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5906,7 +5895,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5924,21 +5913,21 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5961,18 +5950,18 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6020,7 +6009,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6038,21 +6027,21 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6075,17 +6064,17 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6134,7 +6123,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6152,21 +6141,21 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6189,17 +6178,19 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6248,7 +6239,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6266,21 +6257,21 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6303,19 +6294,19 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6364,7 +6355,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6382,21 +6373,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6413,26 +6404,24 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6456,13 +6445,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>297</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6480,7 +6469,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6498,21 +6487,21 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6529,23 +6518,21 @@
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>301</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6570,13 +6557,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6594,7 +6581,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6609,24 +6596,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6640,24 +6627,26 @@
         <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>305</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6682,13 +6671,11 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6706,7 +6693,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6721,24 +6708,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>310</v>
+        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6752,26 +6739,24 @@
         <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>317</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6796,29 +6781,31 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6833,24 +6820,24 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6861,27 +6848,29 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6930,13 +6919,13 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
@@ -6948,7 +6937,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6959,10 +6948,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6973,10 +6962,10 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>77</v>
@@ -6985,17 +6974,15 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>326</v>
+        <v>181</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>327</v>
+        <v>182</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7044,25 +7031,25 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>325</v>
+        <v>184</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>330</v>
+        <v>185</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7073,21 +7060,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7099,15 +7086,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7156,19 +7145,19 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7185,14 +7174,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>155</v>
+        <v>330</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7205,24 +7194,26 @@
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>187</v>
+        <v>331</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>188</v>
+        <v>332</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7270,7 +7261,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>190</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7288,7 +7279,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7299,33 +7290,33 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>335</v>
@@ -7333,11 +7324,9 @@
       <c r="M51" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>159</v>
+        <v>337</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7362,13 +7351,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7386,39 +7373,39 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>130</v>
+        <v>339</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7426,13 +7413,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
@@ -7441,18 +7428,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>182</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
+        <v>183</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7476,11 +7461,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7498,10 +7485,10 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>184</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>87</v>
@@ -7510,27 +7497,27 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>343</v>
+        <v>185</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>344</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7538,10 +7525,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7553,13 +7540,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7598,37 +7585,37 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7639,12 +7626,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7653,10 +7642,10 @@
         <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
@@ -7665,13 +7654,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>345</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>133</v>
+        <v>346</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>134</v>
+        <v>347</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7710,16 +7699,16 @@
         <v>77</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>190</v>
@@ -7751,44 +7740,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C55" t="s" s="2">
         <v>348</v>
       </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K55" t="s" s="2">
-        <v>349</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>350</v>
+        <v>193</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7836,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7848,27 +7839,27 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7879,7 +7870,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7891,19 +7882,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>193</v>
+        <v>280</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>194</v>
+        <v>281</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>195</v>
+        <v>282</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>196</v>
+        <v>283</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7952,13 +7943,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -7970,21 +7961,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>198</v>
+        <v>285</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>199</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8004,22 +7995,20 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>284</v>
+        <v>351</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8068,7 +8057,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>288</v>
+        <v>350</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8086,21 +8075,21 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>289</v>
+        <v>354</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8114,7 +8103,7 @@
         <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>77</v>
@@ -8123,18 +8112,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>357</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8182,7 +8169,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8197,24 +8184,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8228,7 +8215,7 @@
         <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>77</v>
@@ -8237,13 +8224,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>321</v>
+        <v>181</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>360</v>
+        <v>182</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>361</v>
+        <v>183</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8294,7 +8281,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>359</v>
+        <v>184</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8306,38 +8293,38 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>324</v>
+        <v>185</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>363</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8349,15 +8336,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8394,31 +8383,31 @@
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8435,43 +8424,41 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>363</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>187</v>
+        <v>364</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8508,37 +8495,37 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>190</v>
+        <v>366</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>185</v>
+        <v>367</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8549,10 +8536,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8575,13 +8562,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8632,7 +8619,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8650,7 +8637,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8661,10 +8648,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8672,28 +8659,28 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8744,7 +8731,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8759,7 +8746,7 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>376</v>
@@ -8799,13 +8786,13 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>326</v>
+        <v>181</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>378</v>
+        <v>182</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>379</v>
+        <v>183</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8856,7 +8843,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>377</v>
+        <v>184</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8868,13 +8855,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>380</v>
+        <v>185</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8885,21 +8872,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -8911,15 +8898,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8968,19 +8957,19 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8997,14 +8986,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>155</v>
+        <v>330</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9017,24 +9006,26 @@
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>187</v>
+        <v>331</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>188</v>
+        <v>332</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9082,7 +9073,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>190</v>
+        <v>333</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9100,7 +9091,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9111,46 +9102,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>334</v>
+        <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9198,31 +9185,31 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>337</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -9253,13 +9240,13 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>181</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9325,132 +9312,20 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>166</v>
+        <v>388</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K69" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN69">
+  <autoFilter ref="A1:AN68">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9460,7 +9335,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
